--- a/simulation_data/monday_afternoon.xlsx
+++ b/simulation_data/monday_afternoon.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +464,11 @@
           <t>system_time_min</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>service_type</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -493,6 +498,11 @@
       <c r="G2" t="n">
         <v>2.026891950109162</v>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -522,6 +532,11 @@
       <c r="G3" t="n">
         <v>1.263452215698496</v>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,6 +566,11 @@
       <c r="G4" t="n">
         <v>1.516756090713479</v>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -580,6 +600,11 @@
       <c r="G5" t="n">
         <v>3.838611092952992</v>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -609,6 +634,11 @@
       <c r="G6" t="n">
         <v>4.02063032651028</v>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -638,6 +668,11 @@
       <c r="G7" t="n">
         <v>2.53162201801088</v>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -667,6 +702,11 @@
       <c r="G8" t="n">
         <v>2.771248137386713</v>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -696,6 +736,11 @@
       <c r="G9" t="n">
         <v>3.103786204073931</v>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -725,6 +770,11 @@
       <c r="G10" t="n">
         <v>3.909342914994236</v>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -754,6 +804,11 @@
       <c r="G11" t="n">
         <v>1.847405680436161</v>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -783,6 +838,11 @@
       <c r="G12" t="n">
         <v>2.975185212163996</v>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -812,6 +872,11 @@
       <c r="G13" t="n">
         <v>3.464981127310805</v>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -841,6 +906,11 @@
       <c r="G14" t="n">
         <v>0.5420667863554988</v>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -870,6 +940,11 @@
       <c r="G15" t="n">
         <v>0.1853573116916672</v>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -899,6 +974,11 @@
       <c r="G16" t="n">
         <v>1.630454100423529</v>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -928,6 +1008,11 @@
       <c r="G17" t="n">
         <v>1.798239270909439</v>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -957,6 +1042,11 @@
       <c r="G18" t="n">
         <v>3.930380892388557</v>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -986,6 +1076,11 @@
       <c r="G19" t="n">
         <v>1.895178398125332</v>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1015,6 +1110,11 @@
       <c r="G20" t="n">
         <v>2.084307347704285</v>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1044,6 +1144,11 @@
       <c r="G21" t="n">
         <v>3.313413066821191</v>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1073,6 +1178,11 @@
       <c r="G22" t="n">
         <v>2.601469134207132</v>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1102,6 +1212,11 @@
       <c r="G23" t="n">
         <v>1.010778547367808</v>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1131,6 +1246,11 @@
       <c r="G24" t="n">
         <v>2.28852074883822</v>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1160,6 +1280,11 @@
       <c r="G25" t="n">
         <v>2.458504213169546</v>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1189,6 +1314,11 @@
       <c r="G26" t="n">
         <v>1.916175903217902</v>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1218,6 +1348,11 @@
       <c r="G27" t="n">
         <v>2.507418043191217</v>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1247,6 +1382,11 @@
       <c r="G28" t="n">
         <v>2.124741730497297</v>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1276,6 +1416,11 @@
       <c r="G29" t="n">
         <v>2.24798245928292</v>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1305,6 +1450,11 @@
       <c r="G30" t="n">
         <v>2.296744134070096</v>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1334,6 +1484,11 @@
       <c r="G31" t="n">
         <v>1.863284991530279</v>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1363,6 +1518,11 @@
       <c r="G32" t="n">
         <v>2.392943456825436</v>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1392,6 +1552,11 @@
       <c r="G33" t="n">
         <v>3.382296097321544</v>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1421,6 +1586,11 @@
       <c r="G34" t="n">
         <v>3.652432344126413</v>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1450,6 +1620,11 @@
       <c r="G35" t="n">
         <v>0.2895500545909483</v>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1479,6 +1654,11 @@
       <c r="G36" t="n">
         <v>0.7939307080408752</v>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1508,6 +1688,11 @@
       <c r="G37" t="n">
         <v>0.2582249502425851</v>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1537,6 +1722,11 @@
       <c r="G38" t="n">
         <v>1.55669033905905</v>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1566,6 +1756,11 @@
       <c r="G39" t="n">
         <v>0.9580086294219594</v>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1595,6 +1790,11 @@
       <c r="G40" t="n">
         <v>1.546709462983292</v>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1624,6 +1824,11 @@
       <c r="G41" t="n">
         <v>2.472783596271856</v>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1653,6 +1858,11 @@
       <c r="G42" t="n">
         <v>3.00824695303006</v>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1682,6 +1892,11 @@
       <c r="G43" t="n">
         <v>2.038849882196375</v>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1711,6 +1926,11 @@
       <c r="G44" t="n">
         <v>2.26199394711781</v>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1740,6 +1960,11 @@
       <c r="G45" t="n">
         <v>2.380293039786553</v>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1769,6 +1994,11 @@
       <c r="G46" t="n">
         <v>2.076722643395911</v>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1798,6 +2028,11 @@
       <c r="G47" t="n">
         <v>1.898736065855496</v>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1827,6 +2062,11 @@
       <c r="G48" t="n">
         <v>4.750009168641487</v>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1856,6 +2096,11 @@
       <c r="G49" t="n">
         <v>4.39636715285229</v>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1885,6 +2130,11 @@
       <c r="G50" t="n">
         <v>4.129297328576229</v>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1914,6 +2164,11 @@
       <c r="G51" t="n">
         <v>3.967392271023419</v>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1943,6 +2198,11 @@
       <c r="G52" t="n">
         <v>4.602628051458812</v>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1972,6 +2232,11 @@
       <c r="G53" t="n">
         <v>3.833907447723209</v>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2001,6 +2266,11 @@
       <c r="G54" t="n">
         <v>4.573340301252693</v>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2030,6 +2300,11 @@
       <c r="G55" t="n">
         <v>3.8024709918131</v>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2059,6 +2334,11 @@
       <c r="G56" t="n">
         <v>1.580129320779343</v>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2088,6 +2368,11 @@
       <c r="G57" t="n">
         <v>1.007988621668912</v>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2117,6 +2402,11 @@
       <c r="G58" t="n">
         <v>4.445089609369286</v>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2146,6 +2436,11 @@
       <c r="G59" t="n">
         <v>5.010200419891634</v>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2175,6 +2470,11 @@
       <c r="G60" t="n">
         <v>4.319035274963928</v>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2204,6 +2504,11 @@
       <c r="G61" t="n">
         <v>4.047159781280206</v>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2233,6 +2538,11 @@
       <c r="G62" t="n">
         <v>3.531429179708738</v>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2262,6 +2572,11 @@
       <c r="G63" t="n">
         <v>3.131137411237829</v>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2291,6 +2606,11 @@
       <c r="G64" t="n">
         <v>0.7835162041458048</v>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2320,6 +2640,11 @@
       <c r="G65" t="n">
         <v>1.21182280690348</v>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2349,6 +2674,11 @@
       <c r="G66" t="n">
         <v>2.951822828959603</v>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2378,6 +2708,11 @@
       <c r="G67" t="n">
         <v>3.285564398030282</v>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2407,6 +2742,11 @@
       <c r="G68" t="n">
         <v>3.587238725406129</v>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2436,6 +2776,11 @@
       <c r="G69" t="n">
         <v>2.767337008612823</v>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2465,6 +2810,11 @@
       <c r="G70" t="n">
         <v>4.080529607146923</v>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2494,6 +2844,11 @@
       <c r="G71" t="n">
         <v>4.639271378736725</v>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2523,6 +2878,11 @@
       <c r="G72" t="n">
         <v>4.029443528872346</v>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2552,6 +2912,11 @@
       <c r="G73" t="n">
         <v>4.441421802111298</v>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2581,6 +2946,11 @@
       <c r="G74" t="n">
         <v>6.925250983823871</v>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2610,6 +2980,11 @@
       <c r="G75" t="n">
         <v>5.308229870175217</v>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2639,6 +3014,11 @@
       <c r="G76" t="n">
         <v>5.250181184886511</v>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2668,6 +3048,11 @@
       <c r="G77" t="n">
         <v>7.363466836091597</v>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2697,6 +3082,11 @@
       <c r="G78" t="n">
         <v>7.432729774220174</v>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2726,6 +3116,11 @@
       <c r="G79" t="n">
         <v>5.662959755632837</v>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2755,6 +3150,11 @@
       <c r="G80" t="n">
         <v>5.077687193553517</v>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2784,6 +3184,11 @@
       <c r="G81" t="n">
         <v>5.642956471171836</v>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2813,6 +3218,11 @@
       <c r="G82" t="n">
         <v>6.622788363396289</v>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2842,6 +3252,11 @@
       <c r="G83" t="n">
         <v>8.210938437681705</v>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2871,6 +3286,11 @@
       <c r="G84" t="n">
         <v>6.814762278828795</v>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2900,6 +3320,11 @@
       <c r="G85" t="n">
         <v>6.029144410391419</v>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2929,6 +3354,11 @@
       <c r="G86" t="n">
         <v>9.211443964668788</v>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2958,6 +3388,11 @@
       <c r="G87" t="n">
         <v>7.78358537131646</v>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2987,6 +3422,11 @@
       <c r="G88" t="n">
         <v>7.473992641464101</v>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3016,6 +3456,11 @@
       <c r="G89" t="n">
         <v>5.754403765846736</v>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3045,6 +3490,11 @@
       <c r="G90" t="n">
         <v>4.708105263288489</v>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3074,6 +3524,11 @@
       <c r="G91" t="n">
         <v>4.371471803712195</v>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3103,6 +3558,11 @@
       <c r="G92" t="n">
         <v>3.34243190131937</v>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3132,6 +3592,11 @@
       <c r="G93" t="n">
         <v>4.773135402494988</v>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3161,6 +3626,11 @@
       <c r="G94" t="n">
         <v>4.714889495824565</v>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3190,6 +3660,11 @@
       <c r="G95" t="n">
         <v>3.91724803917977</v>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3219,6 +3694,11 @@
       <c r="G96" t="n">
         <v>2.396233405287848</v>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3248,6 +3728,11 @@
       <c r="G97" t="n">
         <v>2.931673527656373</v>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3277,6 +3762,11 @@
       <c r="G98" t="n">
         <v>3.124982340246889</v>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3306,6 +3796,11 @@
       <c r="G99" t="n">
         <v>3.407978314165672</v>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3335,6 +3830,11 @@
       <c r="G100" t="n">
         <v>2.763949587818346</v>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3364,6 +3864,11 @@
       <c r="G101" t="n">
         <v>2.149503913431409</v>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3393,6 +3898,11 @@
       <c r="G102" t="n">
         <v>1.930744255119328</v>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3422,6 +3932,11 @@
       <c r="G103" t="n">
         <v>3.425135106896381</v>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3450,6 +3965,11 @@
       </c>
       <c r="G104" t="n">
         <v>3.615355725806804</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
       </c>
     </row>
   </sheetData>
